--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>1871.573486328125</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1922.800048828125</v>
+      </c>
+      <c r="H2" t="n">
+        <v>51.2265625</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.664164822089571</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.424929609805216</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:29</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1923.0185546875</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>1876.306641,1874.542236,1874.385498,1873.853271,1873.230713,1871.573486</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1862.380005,1891.560059,1901.089966,1897.400024,1903.540039,1922.800049</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>13.926636,17.017823,26.704468,23.546753,30.309326,51.226563</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.747787,0.899671,1.404692,1.241001,1.592261,2.664165</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.424929609805216</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>1874.803223,1875.084229,1873.072266,1872.248291,1871.644775,1865.930664</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>1866.742920,1861.513428,1858.001465,1854.861084,1850.898926,1846.416992</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:29</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1922.953857,1922.458862,1923.073975,1924.119263,1923.680420,1923.018555</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1920.693726,1923.687622,1919.674683,1919.885132,1920.953613,1917.012573</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1900.998291,1891.978516,1883.948364,1877.986328,1869.880493,1863.062012</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1910.008667,1904.419678,1899.202026,1895.658081,1889.581909,1884.985962</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>1923.0185546875</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1930.849975585938</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.8314208984375</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.405594478983846</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3447584707123945</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:30:01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1926.072998046875</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>1922.953857,1922.458862,1923.073975,1924.119263,1923.680420,1923.018555</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1932.890015,1934.609985,1930.760010,1922.640015,1922.800049,1930.849976</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>9.936158,12.151123,7.686035,1.479248,0.880371,7.831421</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.514057,0.628092,0.398083,0.076938,0.045786,0.405594</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3447584707123945</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>1920.693726,1923.687622,1919.674683,1919.885132,1920.953613,1917.012573</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>1910.008667,1904.419678,1899.202026,1895.658081,1889.581909,1884.985962</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:30:01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1929.578857,1927.181641,1926.814941,1927.392334,1925.552979,1926.072998</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1927.754395,1927.271484,1925.885254,1923.749023,1923.845703,1918.705811</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1911.564209,1907.181152,1900.917725,1897.457031,1890.985840,1886.493408</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1917.974854,1915.338135,1911.707031,1910.817383,1903.977539,1901.157471</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>1926.072998046875</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1922.969970703125</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.10302734375</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1613663963049508</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.406753683768711</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:35:01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1918.8974609375</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>1929.578857,1927.181641,1926.814941,1927.392334,1925.552979,1926.072998</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1912.880005,1926.160034,1941.949951,1924.300049,1933.540039,1922.969971</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>16.698852,1.021607,15.135010,3.092285,7.987060,3.103027</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.872969,0.053039,0.779372,0.160697,0.413080,0.161366</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.406753683768711</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>1927.754395,1927.271484,1925.885254,1923.749023,1923.845703,1918.705811</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>1917.974854,1915.338135,1911.707031,1910.817383,1903.977539,1901.157471</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:35:01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1925.344727,1922.782471,1924.034180,1921.798340,1922.919434,1918.897461</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1922.924316,1924.579590,1923.545166,1921.233398,1922.319824,1912.511475</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1907.051758,1902.145264,1897.659180,1891.192139,1890.528076,1882.686279</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1913.325439,1910.810303,1909.199951,1906.035156,1903.451904,1897.019287</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>1918.8974609375</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1878.599975585938</v>
+      </c>
+      <c r="H5" t="n">
+        <v>40.2974853515625</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.145080691752573</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.574457215028795</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:29</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1877.712158203125</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>1925.344727,1922.782471,1924.034180,1921.798340,1922.919434,1918.897461</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1914.199951,1925.260010,1893.800049,1874.140015,1876.910034,1878.599976</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>11.144776,2.477539,30.234131,47.658325,46.009400,40.297485</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.582216,0.128686,1.596480,2.542944,2.451338,2.145081</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.574457215028795</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>1922.924316,1924.579590,1923.545166,1921.233398,1922.319824,1912.511475</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>1913.325439,1910.810303,1909.199951,1906.035156,1903.451904,1897.019287</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:29</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1880.051270,1876.134888,1877.578735,1876.885620,1879.311157,1877.712158</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1876.814575,1877.437866,1877.511353,1878.081177,1876.377563,1874.668823</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1852.195435,1843.595825,1839.719849,1836.296021,1833.261230,1827.446533</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1862.291504,1856.214844,1855.314575,1853.518799,1851.095093,1846.974854</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>1877.712158203125</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1857.829956054688</v>
+      </c>
+      <c r="H6" t="n">
+        <v>19.8822021484375</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.070184172864755</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.829955288961957</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:19</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1852.3310546875</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>1880.051270,1876.134888,1877.578735,1876.885620,1879.311157,1877.712158</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1894.640015,1882.760010,1860.000000,1862.030029,1859.880005,1857.829956</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>14.588745,6.625122,17.578735,14.855591,19.431152,19.882202</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.770001,0.351883,0.945093,0.797817,1.044753,1.070184</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.829955288961957</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>1876.814575,1877.437866,1877.511353,1878.081177,1876.377563,1874.668823</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>1862.291504,1856.214844,1855.314575,1853.518799,1851.095093,1846.974854</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:19</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1855.821045,1853.189331,1853.397949,1849.532715,1851.626343,1852.331055</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1852.449585,1855.776001,1855.002441,1851.529663,1851.358521,1848.134644</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1828.529419,1821.285889,1818.364502,1812.030762,1808.163208,1805.201782</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1835.707031,1833.056030,1830.633911,1825.330322,1823.096802,1821.632568</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>1852.3310546875</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1881.239990234375</v>
+      </c>
+      <c r="H7" t="n">
+        <v>28.908935546875</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.536695780280185</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8001528524732466</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:13</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1888.054931640625</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>1855.821045,1853.189331,1853.397949,1849.532715,1851.626343,1852.331055</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1854.489990,1856.060059,1866.099976,1873.060059,1872.239990,1881.239990</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.331055,2.870728,12.702027,23.527344,20.613647,28.908935</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.071775,0.154668,0.680672,1.256091,1.101015,1.536696</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8001528524732466</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>1852.449585,1855.776001,1855.002441,1851.529663,1851.358521,1848.134644</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>1835.707031,1833.056030,1830.633911,1825.330322,1823.096802,1821.632568</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:13</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1881.894043,1883.229370,1885.170166,1882.183105,1887.204712,1888.054932</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1879.397095,1886.481689,1887.130249,1879.947876,1884.374512,1883.459351</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1858.976929,1856.992432,1854.732910,1847.315063,1849.283081,1845.965576</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1865.300903,1866.873047,1865.606201,1861.819458,1861.718994,1862.168213</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>1888.054931640625</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1945.319946289062</v>
+      </c>
+      <c r="H8" t="n">
+        <v>57.2650146484375</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.943732456847398</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.587157452474757</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:46</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1929.93505859375</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>1881.894043,1883.229370,1885.170166,1882.183105,1887.204712,1888.054932</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1879.849976,1884.229980,1913.290039,1912.479980,1952.890015,1945.319946</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.044067,1.000610,28.119873,30.296875,65.685303,57.265014</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.108736,0.053104,1.469713,1.584167,3.363492,2.943732</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.587157452474757</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>1879.397095,1886.481689,1887.130249,1879.947876,1884.374512,1883.459351</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>1865.300903,1866.873047,1865.606201,1861.819458,1861.718994,1862.168213</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:46</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1949.802734,1949.250244,1938.195801,1934.996826,1946.026123,1929.935059</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1949.784424,1950.490234,1943.869141,1929.804932,1935.153076,1924.354980</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1908.820557,1894.812012,1876.668945,1863.468018,1875.833252,1855.641357</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1916.828369,1913.973145,1898.334229,1892.320801,1900.759033,1884.902344</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>1929.93505859375</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1877.989990234375</v>
+      </c>
+      <c r="H9" t="n">
+        <v>51.945068359375</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.765992823683379</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.344521426854831</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:50</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1799.132934570312</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>1949.802734,1949.250244,1938.195801,1934.996826,1946.026123,1929.935059</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1962.689941,1957.979980,1925.439941,1946.839966,1890.670044,1877.989990</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12.887207,8.729736,12.755860,11.843140,55.356079,51.945069</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.656609,0.445854,0.662491,0.608326,2.927855,2.765993</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.344521426854831</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>1949.784424,1950.490234,1943.869141,1929.804932,1935.153076,1924.354980</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>1916.828369,1913.973145,1898.334229,1892.320801,1900.759033,1884.902344</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:50</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1860.243896,1853.601440,1835.177979,1815.921387,1806.124268,1799.132935</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1855.904053,1857.767334,1836.939331,1820.648315,1802.137939,1796.078979</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1805.450439,1780.174438,1751.725098,1717.979980,1704.978760,1694.515503</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1816.960693,1803.823730,1781.489624,1754.357056,1744.456177,1734.088623</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>1799.132934570312</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1902.910034179688</v>
+      </c>
+      <c r="H10" t="n">
+        <v>103.7770996093755</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.453599894128049</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.770613132576553</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1890.702392578125</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>1860.243896,1853.601440,1835.177979,1815.921387,1806.124268,1799.132935</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1881.880005,1874.790039,1918.300049,1919.510010,1904.400024,1902.910034</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>21.636109,21.188599,83.122070,103.588623,98.275756,103.777099</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.149707,1.130185,4.333111,5.396618,5.160458,5.453600</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3.770613132576553</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>1855.904053,1857.767334,1836.939331,1820.648315,1802.137939,1796.078979</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>1816.960693,1803.823730,1781.489624,1754.357056,1744.456177,1734.088623</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1897.606567,1890.016724,1893.115234,1894.027832,1895.800537,1890.702393</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1891.431152,1894.206177,1891.772949,1896.214355,1889.037598,1887.887207</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1859.901978,1843.121460,1839.373901,1830.927246,1829.123779,1819.485596</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1866.738770,1858.723267,1858.359009,1855.072998,1854.988770,1848.163818</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>1890.702392578125</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1908.56005859375</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17.857666015625</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9356617275530089</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7626975435288649</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:07</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1914.635009765625</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>1897.606567,1890.016724,1893.115234,1894.027832,1895.800537,1890.702393</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1921.280029,1913.010010,1889.810059,1886.619995,1907.989990,1908.560059</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>23.673462,22.993286,3.305175,7.407837,12.189453,17.857666</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.232171,1.201943,0.174895,0.392651,0.638864,0.935662</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7626975435288649</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>1891.431152,1894.206177,1891.772949,1896.214355,1889.037598,1887.887207</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>1866.738770,1858.723267,1858.359009,1855.072998,1854.988770,1848.163818</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:07</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1898.606689,1903.059570,1911.224854,1906.224365,1920.591797,1914.635010</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1889.754150,1907.723389,1906.198730,1905.187256,1912.106689,1899.925049</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1859.399414,1858.599365,1861.087158,1845.727051,1857.680908,1848.560791</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1868.005615,1874.690186,1879.336670,1871.105957,1879.396973,1874.108154</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>1914.635009765625</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1904.06005859375</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10.574951171875</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5553895804991134</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4784925500716923</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:59</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1902.128540039062</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>1898.606689,1903.059570,1911.224854,1906.224365,1920.591797,1914.635010</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1900.459961,1920.550049,1916.699951,1922.079956,1916.819946,1904.060059</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.853272,17.490479,5.475097,15.855591,3.771851,10.574951</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.097517,0.910702,0.285652,0.824918,0.196776,0.555390</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4784925500716923</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>1889.754150,1907.723389,1906.198730,1905.187256,1912.106689,1899.925049</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>1868.005615,1874.690186,1879.336670,1871.105957,1879.396973,1874.108154</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:59</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1897.994751,1902.024170,1912.539429,1908.145264,1907.272583,1902.128540</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1898.215210,1907.608276,1907.315430,1908.240234,1910.661865,1893.254395</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1877.617920,1870.596436,1872.148804,1856.812622,1850.929565,1842.780884</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1880.184448,1886.024170,1890.122437,1880.617920,1875.111450,1867.054321</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>1902.128540039062</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1866.359985351562</v>
+      </c>
+      <c r="H13" t="n">
+        <v>35.76855468749955</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.916487439091869</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.83249681354974</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1861.695556640625</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>1897.994751,1902.024170,1912.539429,1908.145264,1907.272583,1902.128540</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1888.239990,1882.599976,1860.560059,1866.520020,1860.640015,1866.359985</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>9.754761,19.424194,51.979370,41.625244,46.632568,35.768555</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.516606,1.031775,2.793749,2.230099,2.506265,1.916487</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.83249681354974</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>1898.215210,1907.608276,1907.315430,1908.240234,1910.661865,1893.254395</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>1880.184448,1886.024170,1890.122437,1880.617920,1875.111450,1867.054321</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1864.243164,1863.778564,1860.927734,1858.582031,1857.354248,1861.695557</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1861.810303,1863.009277,1868.973877,1862.804932,1853.989258,1857.494873</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1839.857666,1833.139160,1823.868408,1817.692627,1816.630615,1820.621094</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1845.247559,1844.280762,1839.234863,1831.893799,1832.159180,1834.743896</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>1861.695556640625</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1876.510009765625</v>
+      </c>
+      <c r="H14" t="n">
+        <v>14.814453125</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7894683773549558</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5770705407304182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:56</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1862.6328125</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>1864.243164,1863.778564,1860.927734,1858.582031,1857.354248,1861.695557</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1867.680054,1865.189941,1868.439941,1835.550049,1843.410034,1876.510010</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.436890,1.411377,7.512207,23.031982,13.944214,14.814453</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.184019,0.075669,0.402058,1.254773,0.756436,0.789468</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5770705407304182</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>1861.810303,1863.009277,1868.973877,1862.804932,1853.989258,1857.494873</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>1845.247559,1844.280762,1839.234863,1831.893799,1832.159180,1834.743896</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:56</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1872.911621,1868.728516,1866.990723,1863.444336,1864.648926,1862.632812</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1870.067627,1871.186279,1865.569092,1864.352295,1862.115479,1863.020996</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1847.407715,1837.524170,1831.725586,1823.966309,1822.188721,1818.479248</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1856.513672,1848.712646,1844.450684,1837.977051,1836.391357,1833.189209</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>1862.6328125</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1858.920043945312</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.7127685546875</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1997271785185359</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6062371464201043</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1864.9951171875</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>1872.911621,1868.728516,1866.990723,1863.444336,1864.648926,1862.632812</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1874.050049,1850.800049,1857.119995,1880.060059,1883.349976,1858.920044</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.138428,17.928467,9.870728,16.615723,18.701050,3.712768</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.060747,0.968687,0.531507,0.883787,0.992967,0.199727</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6062371464201043</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>1870.067627,1871.186279,1865.569092,1864.352295,1862.115479,1863.020996</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>1856.513672,1848.712646,1844.450684,1837.977051,1836.391357,1833.189209</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1860.106812,1863.601440,1865.630615,1865.050781,1865.436768,1864.995117</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1858.547241,1864.202881,1865.716797,1867.385132,1864.758301,1864.829224</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1839.064941,1836.837524,1834.615845,1831.374512,1826.956543,1825.873535</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1847.037598,1847.175537,1846.457886,1843.598389,1841.830811,1839.197510</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>1864.9951171875</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1858.0400390625</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.955078125</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.37432337187466</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5997568165203041</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1855.734008789062</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>1860.106812,1863.601440,1865.630615,1865.050781,1865.436768,1864.995117</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1841.430054,1837.400024,1861.099976,1868.569946,1858.890015,1858.040039</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>18.676758,26.201416,4.530639,3.519165,6.546753,6.955078</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.014253,1.426005,0.243439,0.188335,0.352186,0.374323</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5997568165203041</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>1858.547241,1864.202881,1865.716797,1867.385132,1864.758301,1864.829224</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>1847.037598,1847.175537,1846.457886,1843.598389,1841.830811,1839.197510</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1860.109497,1859.283081,1858.695923,1856.600708,1856.770264,1855.734009</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1860.217773,1860.383179,1856.074707,1857.440308,1857.427124,1854.642212</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1838.209961,1832.244629,1827.307007,1822.479614,1819.254395,1817.659912</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1847.043579,1842.580444,1839.453857,1835.173828,1833.744385,1831.443115</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>1855.734008789062</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1864.68994140625</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8.955932617187955</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4802907131270235</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6295092895359595</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1865.135498046875</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>1860.109497,1859.283081,1858.695923,1856.600708,1856.770264,1855.734009</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1862.079956,1870.829956,1871.410034,1873.680054,1875.199951,1864.689941</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.970459,11.546875,12.714111,17.079346,18.429687,8.955932</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.105820,0.617206,0.679387,0.911540,0.982812,0.480291</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6295092895359595</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>1860.217773,1860.383179,1856.074707,1857.440308,1857.427124,1854.642212</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>1847.043579,1842.580444,1839.453857,1835.173828,1833.744385,1831.443115</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1865.041748,1864.072266,1864.227295,1862.880371,1864.426025,1865.135498</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1865.771973,1864.421143,1862.363037,1861.775635,1865.433594,1862.385010</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1844.337646,1837.632568,1833.496094,1828.575439,1827.334717,1826.150635</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1852.138672,1848.143799,1845.879639,1842.002197,1841.596191,1841.100586</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>1865.135498046875</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1895.489990234375</v>
+      </c>
+      <c r="H18" t="n">
+        <v>30.3544921875</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.601406092561148</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.249883720151755</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:56</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1889.679443359375</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>1865.041748,1864.072266,1864.227295,1862.880371,1864.426025,1865.135498</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1870.609985,1867.109985,1872.410034,1915.619995,1907.290039,1895.489990</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5.568237,3.037719,8.182739,52.739624,42.864014,30.354492</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.297670,0.162696,0.437016,2.753136,2.247378,1.601406</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1.249883720151755</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>1865.771973,1864.421143,1862.363037,1861.775635,1865.433594,1862.385010</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>1852.138672,1848.143799,1845.879639,1842.002197,1841.596191,1841.100586</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:56</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1893.464600,1893.040405,1891.678589,1891.075806,1889.361084,1889.679443</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1892.457886,1890.840088,1891.407349,1889.018921,1888.164185,1887.025024</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1873.244385,1866.435791,1860.103760,1855.758667,1852.020386,1850.171997</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1880.689087,1876.372437,1871.561279,1869.182251,1865.438232,1864.779053</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>1889.679443359375</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1901.52001953125</v>
+      </c>
+      <c r="H19" t="n">
+        <v>11.840576171875</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6226900611224624</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7544036596092552</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:08</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1893.534545898438</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>1893.464600,1893.040405,1891.678589,1891.075806,1889.361084,1889.679443</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1907.119995,1905.839966,1909.109985,1908.569946,1902.420044,1901.520020</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>13.655395,12.799561,17.431396,17.494140,13.058960,11.840577</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.716022,0.671597,0.913064,0.916610,0.686439,0.622690</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7544036596092552</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>1892.457886,1890.840088,1891.407349,1889.018921,1888.164185,1887.025024</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>1880.689087,1876.372437,1871.561279,1869.182251,1865.438232,1864.779053</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:08</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1901.986938,1900.008179,1901.390747,1898.843140,1898.310303,1893.534546</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1899.897339,1895.074829,1899.752563,1898.288818,1897.449585,1887.552734</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1880.515137,1870.894653,1866.547974,1858.472900,1854.952515,1845.194580</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1887.889282,1882.486816,1880.304932,1874.682129,1871.579346,1864.290283</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>1893.534545898438</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1913.449951171875</v>
+      </c>
+      <c r="H20" t="n">
+        <v>19.91540527343705</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.040811402526627</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7745096767185773</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1904.7421875</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>1901.986938,1900.008179,1901.390747,1898.843140,1898.310303,1893.534546</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1900.930054,1914.890015,1916.589966,1918.099976,1917.030029,1913.449951</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.056884,14.881836,15.199219,19.256836,18.719726,19.915405</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.055598,0.777164,0.793034,1.003954,0.976496,1.040811</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7745096767185773</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>1899.897339,1895.074829,1899.752563,1898.288818,1897.449585,1887.552734</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>1887.889282,1882.486816,1880.304932,1874.682129,1871.579346,1864.290283</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1913.800903,1912.501587,1910.800537,1909.421509,1908.046753,1904.742188</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1911.618774,1908.096191,1908.170288,1905.226318,1905.294434,1900.281738</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1890.860352,1883.634888,1876.374268,1871.490234,1866.920044,1860.531738</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1900.189087,1895.541260,1889.909424,1887.239868,1882.663696,1877.971680</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>1904.7421875</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1914.550048828125</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.807861328125</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5122802265800408</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4038106703565147</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1912.03173828125</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>1913.800903,1912.501587,1910.800537,1909.421509,1908.046753,1904.742188</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1914.270020,1919.609985,1921.239990,1919.160034,1916.959961,1914.550049</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.469117,7.108398,10.439453,9.738525,8.913208,9.807861</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.024506,0.370304,0.543371,0.507437,0.464966,0.512280</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4038106703565147</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>1911.618774,1908.096191,1908.170288,1905.226318,1905.294434,1900.281738</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>1900.189087,1895.541260,1889.909424,1887.239868,1882.663696,1877.971680</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1914.711304,1913.138306,1913.166992,1912.537109,1912.761841,1912.031738</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1913.658447,1909.750244,1911.572754,1909.834229,1909.992798,1907.695068</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1898.111572,1892.219849,1888.260986,1884.680664,1882.300903,1879.210083</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1905.532837,1901.251343,1898.409668,1896.768555,1894.792480,1893.190308</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>1912.03173828125</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1914.06005859375</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.0283203125</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1059695229203098</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2845720339660216</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1910.603759765625</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>1914.711304,1913.138306,1913.166992,1912.537109,1912.761841,1912.031738</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1917.500000,1917.930054,1924.640015,1920.560059,1909.089966,1914.060059</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.788696,4.791748,11.473023,8.022950,3.671875,2.028321</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.145434,0.249840,0.596113,0.417740,0.192336,0.105970</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2845720339660216</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>1913.658447,1909.750244,1911.572754,1909.834229,1909.992798,1907.695068</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>1905.532837,1901.251343,1898.409668,1896.768555,1894.792480,1893.190308</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1915.061768,1913.437744,1912.075928,1911.890869,1912.404297,1910.603760</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1913.641113,1912.009033,1910.729980,1909.989746,1910.882324,1907.254150</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1896.831543,1890.758301,1885.885742,1882.598877,1880.453857,1876.646973</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1905.087402,1900.403809,1896.141113,1895.013184,1893.033447,1890.476807</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>1910.603759765625</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1876.280029296875</v>
+      </c>
+      <c r="H23" t="n">
+        <v>34.32373046875</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.829350093419297</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.421206789968425</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:15:05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1879.782958984375</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>1915.061768,1913.437744,1912.075928,1911.890869,1912.404297,1910.603760</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1923.979980,1918.500000,1875.020020,1876.640015,1872.780029,1876.280029</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>8.918212,5.062256,37.055908,35.250854,39.624268,34.323731</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.463529,0.263865,1.976294,1.878403,2.115799,1.829350</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1.421206789968425</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>1913.641113,1912.009033,1910.729980,1909.989746,1910.882324,1907.254150</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>1905.087402,1900.403809,1896.141113,1895.013184,1893.033447,1890.476807</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:15:05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1876.130371,1876.584717,1877.876709,1878.556885,1879.873047,1879.782959</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1874.513184,1875.289062,1878.090820,1878.634277,1880.344238,1879.065186</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1854.580811,1849.203125,1845.387695,1841.822510,1839.662109,1836.872314</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1863.453369,1859.584473,1857.199707,1855.915527,1854.306641,1852.510498</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>1879.782958984375</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1883.640014648438</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.8570556640625</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2047660717582696</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3482372664826009</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:51</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1880.412475585938</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>1876.130371,1876.584717,1877.876709,1878.556885,1879.873047,1879.782959</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1876.010010,1891.420044,1861.199951,1879.689941,1877.290039,1883.640015</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.120361,14.835327,16.676758,1.133056,2.583008,3.857056</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.006416,0.784349,0.896022,0.060279,0.137592,0.204766</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3482372664826009</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>1874.513184,1875.289062,1878.090820,1878.634277,1880.344238,1879.065186</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>1863.453369,1859.584473,1857.199707,1855.915527,1854.306641,1852.510498</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:51</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1881.327759,1881.238159,1880.929688,1879.888672,1880.503174,1880.412476</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1880.675781,1879.504883,1881.197632,1879.981934,1879.748169,1878.122803</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1859.483398,1854.860229,1850.714722,1846.508911,1844.976929,1842.708374</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1868.074463,1865.241455,1861.758423,1859.741577,1858.100952,1856.746948</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>1880.412475585938</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1872.989990234375</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7.422485351562955</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3962907111230289</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5624454274709746</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:18</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1879.588989257812</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>1881.327759,1881.238159,1880.929688,1879.888672,1880.503174,1880.412476</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1890.010010,1913.910034,1890.699951,1877.170044,1877.680054,1872.989990</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>8.682251,32.671875,9.770263,2.718628,2.823120,7.422486</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.459376,1.707075,0.516754,0.144826,0.150352,0.396291</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5624454274709746</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>1880.675781,1879.504883,1881.197632,1879.981934,1879.748169,1878.122803</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>1868.074463,1865.241455,1861.758423,1859.741577,1858.100952,1856.746948</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:18</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1875.443481,1876.528442,1877.761963,1878.472168,1879.469604,1879.588989</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1875.951294,1877.447998,1878.638306,1879.936279,1880.814819,1880.927612</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1857.918457,1855.525024,1853.775757,1851.974487,1850.952759,1848.994995</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1864.954224,1863.533081,1862.489258,1862.188477,1861.248169,1860.307495</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>1879.588989257812</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1887.089965820312</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.500976562500455</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3974890809850606</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3960829707262134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:33:06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1889.8857421875</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>1875.443481,1876.528442,1877.761963,1878.472168,1879.469604,1879.588989</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1893.869995,1878.349976,1878.390015,1885.310059,1889.160034,1887.089966</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>18.426514,1.821534,0.628052,6.837891,9.690430,7.500977</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.972956,0.096975,0.033436,0.362693,0.512949,0.397489</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3960829707262134</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>1875.951294,1877.447998,1878.638306,1879.936279,1880.814819,1880.927612</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>1864.954224,1863.533081,1862.489258,1862.188477,1861.248169,1860.307495</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:33:06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1888.912598,1889.442261,1889.377808,1889.255981,1889.306396,1889.885742</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1889.449585,1889.146118,1889.743286,1889.538940,1889.696899,1890.135864</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1873.601074,1870.958984,1868.311646,1866.393921,1864.500610,1863.260620</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1879.786133,1878.096191,1876.120972,1875.045898,1873.504639,1873.173828</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>1889.8857421875</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1882.130004882812</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7.7557373046875</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4120723480613337</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6361084197267779</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:43:05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1885.562255859375</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>1888.912598,1889.442261,1889.377808,1889.255981,1889.306396,1889.885742</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1871.180054,1876.410034,1879.239990,1879.040039,1876.560059,1882.130005</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>17.732544,13.032227,10.137818,10.215942,12.746337,7.755737</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.947666,0.694530,0.539464,0.543679,0.679240,0.412072</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6361084197267779</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>1889.449585,1889.146118,1889.743286,1889.538940,1889.696899,1890.135864</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>1879.786133,1878.096191,1876.120972,1875.045898,1873.504639,1873.173828</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:43:05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1881.413086,1881.993774,1883.152466,1884.206299,1885.502197,1885.562256</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1881.512573,1882.005249,1883.663330,1885.470703,1885.844482,1886.118042</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1866.397217,1864.209473,1863.191895,1862.676514,1862.624634,1860.979370</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1872.261719,1871.006836,1870.467773,1870.972290,1871.057617,1870.195679</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>1885.562255859375</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1877.859985351562</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7.7022705078125</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4101621296526282</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1941728309889162</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:50:06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1877.235473632812</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>1881.413086,1881.993774,1883.152466,1884.206299,1885.502197,1885.562256</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1878.560059,1877.290039,1882.890015,1882.359985,1880.979980,1877.859985</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.853027,4.703735,0.262451,1.846314,4.522217,7.702271</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.151873,0.250560,0.013939,0.098085,0.240418,0.410162</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1941728309889162</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>1881.512573,1882.005249,1883.663330,1885.470703,1885.844482,1886.118042</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>1872.261719,1871.006836,1870.467773,1870.972290,1871.057617,1870.195679</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:50:06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1878.015869,1877.884033,1877.863281,1877.764526,1877.654175,1877.235474</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1877.930542,1878.926636,1878.832275,1878.486328,1878.283325,1878.671021</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1869.527954,1867.316528,1865.484375,1864.166382,1862.528687,1860.592896</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1873.035400,1871.227417,1869.627441,1869.174194,1867.890869,1866.862793</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>1877.235473632812</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1890.989990234375</v>
+      </c>
+      <c r="H29" t="n">
+        <v>13.75451660156295</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7273712009368266</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.2662657329456683</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:38</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1885.639892578125</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>1878.015869,1877.884033,1877.863281,1877.764526,1877.654175,1877.235474</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1879.300049,1878.910034,1882.010010,1884.150024,1874.130005,1890.989990</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1.284180,1.026001,4.146729,6.385498,3.524170,13.754516</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.068333,0.054606,0.220335,0.338906,0.188043,0.727371</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.2662657329456683</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>1877.930542,1878.926636,1878.832275,1878.486328,1878.283325,1878.671021</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>1873.035400,1871.227417,1869.627441,1869.174194,1867.890869,1866.862793</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:38</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1887.384399,1886.705811,1885.669434,1885.980835,1885.605591,1885.639893</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1887.269165,1887.230957,1886.352173,1886.256836,1886.358765,1886.444214</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1877.652100,1875.122314,1872.500732,1871.842773,1870.369629,1869.455933</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1881.331299,1879.316650,1877.073975,1877.001099,1875.645142,1875.159790</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>1885.639892578125</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1902.760009765625</v>
+      </c>
+      <c r="H30" t="n">
+        <v>17.1201171875</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8997517868587533</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9669918248406368</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:58</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1896.503540039062</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>1887.384399,1886.705811,1885.669434,1885.980835,1885.605591,1885.639893</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1899.140015,1902.699951,1911.459961,1905.670044,1905.810059,1902.760010</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>11.755616,15.994140,25.790527,19.689209,20.204468,17.120117</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.618997,0.840602,1.349258,1.033191,1.060151,0.899752</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9669918248406368</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>1887.269165,1887.230957,1886.352173,1886.256836,1886.358765,1886.444214</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>1881.331299,1879.316650,1877.073975,1877.001099,1875.645142,1875.159790</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:58</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1902.505127,1901.134766,1899.616821,1898.707886,1897.492798,1896.503540</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1901.336914,1899.851074,1899.466553,1897.797119,1896.179443,1896.117554</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1890.345581,1886.161865,1882.056274,1879.411133,1876.075928,1873.362793</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1895.187500,1891.802368,1888.438965,1886.591064,1883.975342,1881.857666</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>1896.503540039062</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1912.589965820312</v>
+      </c>
+      <c r="H31" t="n">
+        <v>16.08642578125045</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8410807370491963</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6147979600817908</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:43</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1909.39306640625</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>1902.505127,1901.134766,1899.616821,1898.707886,1897.492798,1896.503540</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1896.939941,1901.209961,1916.469971,1912.199951,1915.989990,1912.589966</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>5.565186,0.075195,16.853150,13.492065,18.497192,16.086426</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.293377,0.003955,0.879385,0.705578,0.965412,0.841081</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6147979600817908</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>1901.336914,1899.851074,1899.466553,1897.797119,1896.179443,1896.117554</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>1895.187500,1891.802368,1888.438965,1886.591064,1883.975342,1881.857666</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:43</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1912.516479,1912.104736,1911.048340,1910.994263,1910.041260,1909.393066</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1911.245117,1910.765747,1909.719849,1908.371948,1907.579468,1906.854736</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1899.111084,1895.581299,1891.104004,1888.945312,1886.058716,1883.643677</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1904.501587,1902.154419,1899.011108,1897.732056,1895.225952,1893.418945</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>1909.39306640625</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2264.409912109375</v>
+      </c>
+      <c r="H32" t="n">
+        <v>355.016845703125</v>
+      </c>
+      <c r="I32" t="n">
+        <v>15.67811745588124</v>
+      </c>
+      <c r="J32" t="n">
+        <v>8.14999219566314</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:43</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2168.68798828125</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>1912.516479,1912.104736,1911.048340,1910.994263,1910.041260,1909.393066</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1914.459961,1921.550049,2085.350098,2101.929932,2252.050049,2264.409912</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1.943482,9.445313,174.301758,190.935669,342.008789,355.016846</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.101516,0.491547,8.358393,9.083827,15.186554,15.678117</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>8.14999219566314</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>1911.245117,1910.765747,1909.719849,1908.371948,1907.579468,1906.854736</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>1904.501587,1902.154419,1899.011108,1897.732056,1895.225952,1893.418945</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:43</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2255.528320,2242.154785,2221.212402,2201.288086,2182.603516,2168.687988</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2244.118896,2221.227539,2199.893311,2179.757080,2156.676270,2143.681885</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2163.171875,2124.925293,2084.904297,2045.988037,2017.087646,1992.999512</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2197.396973,2168.501465,2133.179688,2104.837891,2074.709961,2054.579834</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>2168.68798828125</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2373.139892578125</v>
+      </c>
+      <c r="H33" t="n">
+        <v>204.451904296875</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8.615248723275352</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.518075460310552</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:49:02</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2353.08154296875</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>2255.528320,2242.154785,2221.212402,2201.288086,2182.603516,2168.687988</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2249.959961,2294.830078,2325.939941,2323.469971,2326.600098,2373.139893</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5.568359,52.675293,104.727539,122.181885,143.996582,204.451905</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.247487,2.295390,4.502590,5.258595,6.189142,8.615249</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>4.518075460310552</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>2244.118896,2221.227539,2199.893311,2179.757080,2156.676270,2143.681885</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>2197.396973,2168.501465,2133.179688,2104.837891,2074.709961,2054.579834</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:49:02</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2370.980957,2366.419922,2364.004395,2363.984131,2357.361816,2353.081543</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2362.662598,2342.950684,2345.454590,2339.767578,2323.729004,2315.361572</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2305.322266,2271.978027,2243.915039,2216.188721,2182.828125,2155.693848</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2333.375488,2312.066895,2290.617188,2277.972168,2249.574707,2231.118896</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>2353.08154296875</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2516.0400390625</v>
+      </c>
+      <c r="H34" t="n">
+        <v>162.95849609375</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.476784691966582</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.536682165906921</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:42:06</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2516.564697265625</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>2370.980957,2366.419922,2364.004395,2363.984131,2357.361816,2353.081543</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2369.979980,2369.850098,2392.889893,2413.209961,2489.540039,2516.040039</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1.000977,3.430176,28.885498,49.225830,132.178223,162.958496</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.042236,0.144742,1.207139,2.039849,5.309343,6.476785</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>2.536682165906921</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>2362.662598,2342.950684,2345.454590,2339.767578,2323.729004,2315.361572</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>2333.375488,2312.066895,2290.617188,2277.972168,2249.574707,2231.118896</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:42:06</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2517.805664,2518.950195,2520.427979,2521.860352,2516.103760,2516.564697</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2512.066406,2491.331543,2503.690918,2493.446777,2486.261475,2481.082275</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2442.675293,2410.724609,2380.713867,2343.580811,2309.514893,2279.732910</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2472.768311,2457.678223,2433.323975,2420.666748,2388.269775,2372.687256</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>2516.564697265625</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2427.139892578125</v>
+      </c>
+      <c r="H35" t="n">
+        <v>89.4248046875</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3.684369613838465</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.87926575014147</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:59</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2423.25390625</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>2517.805664,2518.950195,2520.427979,2521.860352,2516.103760,2516.564697</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2432.760010,2424.020020,2410.469971,2439.000000,2414.219971,2427.139893</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>85.045654,94.930175,109.958008,82.860352,101.883789,89.424804</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3.495851,3.916229,4.561683,3.397308,4.220154,3.684370</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3.87926575014147</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>2512.066406,2491.331543,2503.690918,2493.446777,2486.261475,2481.082275</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>2472.768311,2457.678223,2433.323975,2420.666748,2388.269775,2372.687256</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:59</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2429.054199,2426.082764,2427.294434,2428.614990,2423.285645,2423.253906</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2416.972168,2408.332275,2412.696777,2407.351562,2392.673340,2385.300293</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2377.360596,2351.072754,2327.759766,2303.642090,2277.093506,2252.517090</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2401.586426,2385.136963,2369.680908,2359.656494,2338.004395,2322.804443</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>2423.25390625</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2437.610107421875</v>
+      </c>
+      <c r="H36" t="n">
+        <v>14.356201171875</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5889457517493951</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8877587674086649</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:37</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2426.048828125</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>2429.054199,2426.082764,2427.294434,2428.614990,2423.285645,2423.253906</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2388.419922,2433.360107,2438.389893,2444.459961,2463.540039,2437.610107</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>40.634277,7.277343,11.095459,15.844971,40.254394,14.356201</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1.701304,0.299066,0.455032,0.648199,1.634006,0.588946</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8877587674086649</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>2416.972168,2408.332275,2412.696777,2407.351562,2392.673340,2385.300293</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>2401.586426,2385.136963,2369.680908,2359.656494,2338.004395,2322.804443</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:37</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2441.369629,2436.877930,2434.643799,2431.922607,2428.224854,2426.048828</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2435.336670,2420.940918,2422.147461,2415.796875,2413.678711,2406.803955</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2379.824463,2358.558105,2336.311035,2318.696289,2296.188721,2280.423340</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2408.267822,2393.940674,2378.769531,2370.145020,2354.233154,2344.928223</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>2426.048828125</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2495.469970703125</v>
+      </c>
+      <c r="H37" t="n">
+        <v>69.421142578125</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.781886514088761</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.905794036863967</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:57</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2501.72998046875</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>2441.369629,2436.877930,2434.643799,2431.922607,2428.224854,2426.048828</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2454.229980,2494.129883,2487.209961,2469.820068,2482.479980,2495.469971</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>12.860351,57.251953,52.566162,37.897461,54.255126,69.421143</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.524008,2.295468,2.113459,1.534422,2.185521,2.781887</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1.905794036863967</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>2435.336670,2420.940918,2422.147461,2415.796875,2413.678711,2406.803955</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>2408.267822,2393.940674,2378.769531,2370.145020,2354.233154,2344.928223</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:57</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2491.742432,2498.862305,2495.156006,2497.698975,2496.764648,2501.729980</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2489.522461,2487.145508,2483.893555,2484.672119,2495.853027,2492.028809</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2452.216309,2446.868652,2431.236572,2421.911377,2413.035889,2413.125244</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2471.420166,2471.685547,2458.364258,2459.217041,2452.809814,2451.726074</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>2501.72998046875</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2455.659912109375</v>
+      </c>
+      <c r="H38" t="n">
+        <v>46.070068359375</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.876076900233367</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.166774677101003</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2424.419677734375</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>2491.742432,2498.862305,2495.156006,2497.698975,2496.764648,2501.729980</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2478.120117,2477.520020,2483.350098,2463.669922,2451.250000,2455.659912</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>13.622315,21.342285,11.805908,34.029053,45.514648,46.070068</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.549704,0.861437,0.475402,1.381234,1.856793,1.876077</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1.166774677101003</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>2489.522461,2487.145508,2483.893555,2484.672119,2495.853027,2492.028809</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>2471.420166,2471.685547,2458.364258,2459.217041,2452.809814,2451.726074</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2451.218994,2448.722412,2445.986328,2441.611816,2434.703369,2424.419678</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2444.324219,2425.401367,2415.155029,2404.291504,2383.409912,2363.114746</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2403.095459,2367.039551,2327.497803,2288.243408,2255.173096,2216.563965</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2428.211426,2405.821045,2380.105713,2359.233887,2333.033447,2304.339111</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>2424.419677734375</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2492.580078125</v>
+      </c>
+      <c r="H39" t="n">
+        <v>68.160400390625</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.734532021209825</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.31644186732837</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2529.431884765625</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>2451.218994,2448.722412,2445.986328,2441.611816,2434.703369,2424.419678</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2461.330078,2462.310059,2450.090088,2469.790039,2507.239990,2492.580078</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10.111084,13.587647,4.103760,28.178223,72.536621,68.160400</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.410798,0.551825,0.167494,1.140916,2.893086,2.734532</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1.31644186732837</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>2444.324219,2425.401367,2415.155029,2404.291504,2383.409912,2363.114746</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>2428.211426,2405.821045,2380.105713,2359.233887,2333.033447,2304.339111</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2528.654053,2530.125488,2530.000488,2532.356201,2527.060303,2529.431885</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2529.814209,2524.776611,2517.018066,2527.097656,2524.043213,2511.345459</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2499.891113,2491.958984,2477.428711,2470.916992,2452.359131,2450.280762</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2513.770020,2511.136475,2500.295410,2501.197021,2489.236816,2484.364014</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>2529.431884765625</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2509.1201171875</v>
+      </c>
+      <c r="H40" t="n">
+        <v>20.311767578125</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.80951754517407</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9882507979615032</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:27</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2501.22021484375</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>2528.654053,2530.125488,2530.000488,2532.356201,2527.060303,2529.431885</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2522.020020,2499.159912,2511.729980,2490.750000,2496.600098,2509.120117</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6.634033,30.965576,18.270508,41.606201,30.460205,20.311768</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.263044,1.239039,0.727407,1.670429,1.220067,0.809518</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9882507979615032</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>2529.814209,2524.776611,2517.018066,2527.097656,2524.043213,2511.345459</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>2513.770020,2511.136475,2500.295410,2501.197021,2489.236816,2484.364014</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:27</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2505.788818,2506.888672,2501.315674,2503.526611,2498.549072,2501.220215</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2502.217285,2499.662842,2492.530029,2492.802979,2496.760010,2479.014648</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2477.412842,2476.204834,2460.023193,2459.341064,2450.498291,2457.230225</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2493.212402,2494.539307,2480.177002,2485.772705,2479.344482,2480.968262</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>2501.22021484375</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2435.570068359375</v>
+      </c>
+      <c r="H41" t="n">
+        <v>65.650146484375</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.695473529472203</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.462172818386349</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:52:02</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2426.17138671875</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>2505.788818,2506.888672,2501.315674,2503.526611,2498.549072,2501.220215</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2472.100098,2435.679932,2442.790039,2435.110107,2435.570068,2435.570068</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>33.688720,71.208740,58.525635,68.416504,62.979004,65.650147</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1.362757,2.923567,2.395852,2.809586,2.585801,2.695474</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2.462172818386349</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>2502.217285,2499.662842,2492.530029,2492.802979,2496.760010,2479.014648</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>2493.212402,2494.539307,2480.177002,2485.772705,2479.344482,2480.968262</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:52:02</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2434.401367,2434.617188,2430.404785,2430.130859,2426.305420,2426.171387</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2427.988770,2418.602539,2421.774902,2413.946289,2413.892090,2405.604248</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2389.479004,2381.383301,2362.029297,2354.707520,2338.701172,2333.435059</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2409.606689,2405.941406,2391.389648,2389.645264,2380.164062,2375.426025</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>2426.17138671875</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2457.9599609375</v>
+      </c>
+      <c r="H42" t="n">
+        <v>31.78857421875</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.293290969907638</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8471327161351581</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:46</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2456.181396484375</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>2434.401367,2434.617188,2430.404785,2430.130859,2426.305420,2426.171387</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2435.870117,2444.790039,2453.399902,2457.469971,2457.350098,2457.959961</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1.468750,10.172851,22.995117,27.339112,31.044678,31.788574</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.060297,0.416103,0.937276,1.112490,1.263340,1.293291</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8471327161351581</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>2427.988770,2418.602539,2421.774902,2413.946289,2413.892090,2405.604248</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>2409.606689,2405.941406,2391.389648,2389.645264,2380.164062,2375.426025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:46</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2456.557861,2456.369873,2458.561768,2458.113281,2458.533936,2456.181396</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2450.896240,2448.101562,2452.353271,2440.932861,2450.069824,2441.187988</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2427.543945,2414.585449,2405.337891,2396.191406,2381.299805,2369.313965</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2441.387207,2434.792236,2430.371826,2425.442383,2418.963379,2409.245605</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>2456.181396484375</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2422.389892578125</v>
+      </c>
+      <c r="H43" t="n">
+        <v>33.79150390625</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.394965525978398</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.258773706640323</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:18</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2421.369384765625</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>2456.557861,2456.369873,2458.561768,2458.113281,2458.533936,2456.181396</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2460.010010,2481.020020,2503.590088,2417.810059,2420.810059,2422.389893</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3.452149,24.650147,45.028320,40.303222,37.723877,33.791503</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.140331,0.993549,1.798550,1.666931,1.558316,1.394966</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1.258773706640323</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>2450.896240,2448.101562,2452.353271,2440.932861,2450.069824,2441.187988</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>2441.387207,2434.792236,2430.371826,2425.442383,2418.963379,2409.245605</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:18</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2420.487305,2420.950928,2424.269287,2425.413818,2423.458984,2421.369385</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2414.574219,2404.528076,2410.260254,2399.731934,2401.867676,2393.020264</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2384.834717,2367.948486,2354.525879,2340.614258,2320.017334,2300.563965</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2400.887695,2392.206299,2386.065430,2380.331543,2367.850342,2354.662109</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>2421.369384765625</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2471.699951171875</v>
+      </c>
+      <c r="H44" t="n">
+        <v>50.33056640625</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.036273309888905</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.816701080216205</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:49:06</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2467.11279296875</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>2420.487305,2420.950928,2424.269287,2425.413818,2423.458984,2421.369385</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2445.750000,2467.219971,2481.600098,2467.290039,2471.610107,2471.699951</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>25.262695,46.269043,57.330811,41.876221,48.151123,50.330566</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.032922,1.875351,2.310236,1.697256,1.948168,2.036273</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.816701080216205</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>2414.574219,2404.528076,2410.260254,2399.731934,2401.867676,2393.020264</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>2400.887695,2392.206299,2386.065430,2380.331543,2367.850342,2354.662109</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:49:06</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2473.627441,2471.218994,2471.059814,2470.319580,2467.386475,2467.112793</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2470.726318,2458.902344,2467.593506,2460.872070,2457.852051,2456.154541</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2443.977539,2435.994385,2428.953857,2425.611084,2416.101074,2407.938232</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2456.235596,2451.997559,2446.732666,2446.616455,2440.031982,2437.131592</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>2467.11279296875</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2407.97998046875</v>
+      </c>
+      <c r="H45" t="n">
+        <v>59.1328125</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.455701998340073</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.808713101019914</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2408.25830078125</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>2473.627441,2471.218994,2471.059814,2470.319580,2467.386475,2467.112793</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2458.320068,2448.020020,2417.800049,2412.949951,2413.189941,2407.979980</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>15.307373,23.198974,53.259765,57.369629,54.196534,59.132813</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.622676,0.947663,2.202819,2.377572,2.245846,2.455702</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.808713101019914</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>2470.726318,2458.902344,2467.593506,2460.872070,2457.852051,2456.154541</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>2456.235596,2451.997559,2446.732666,2446.616455,2440.031982,2437.131592</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2409.566162,2411.299561,2412.484863,2413.105957,2411.519287,2408.258301</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2404.362305,2405.311523,2408.426270,2400.270996,2398.290771,2397.182373</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2377.150635,2373.752441,2365.005371,2362.144043,2350.318848,2338.774414</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2389.722900,2388.993164,2383.842773,2382.995361,2374.893799,2371.326660</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>2408.25830078125</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2404.739990234375</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.518310546875</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1463073164318315</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7379068283072387</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:12</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2401.470458984375</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>2409.566162,2411.299561,2412.484863,2413.105957,2411.519287,2408.258301</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2380.500000,2390.159912,2391.909912,2390.830078,2402.300049,2404.739990</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>29.066162,21.139649,20.574951,22.275879,9.219238,3.518311</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1.221011,0.884445,0.860189,0.931722,0.383767,0.146307</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7379068283072387</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>2404.362305,2405.311523,2408.426270,2400.270996,2398.290771,2397.182373</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>2389.722900,2388.993164,2383.842773,2382.995361,2374.893799,2371.326660</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:12</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2405.282227,2405.578125,2405.131104,2405.350342,2403.255127,2401.470459</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2401.219727,2402.209473,2408.078857,2396.801270,2397.413086,2392.432373</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2369.774170,2371.297363,2367.617676,2370.456299,2366.539795,2359.395508</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2382.109131,2383.509766,2380.793701,2383.389160,2377.426270,2377.271484</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>2401.470458984375</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2503.68994140625</v>
+      </c>
+      <c r="H47" t="n">
+        <v>102.219482421875</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.082753248769346</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.526646332970157</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:53</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2492.752197265625</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>2405.282227,2405.578125,2405.131104,2405.350342,2403.255127,2401.470459</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2405.770020,2516.979980,2518.260010,2507.739990,2504.840088,2503.689941</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.487793,111.401855,113.128906,102.389648,101.584961,102.219482</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.020276,4.426013,4.492344,4.082945,4.055547,4.082753</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>3.526646332970157</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>2401.219727,2402.209473,2408.078857,2396.801270,2397.413086,2392.432373</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>2382.109131,2383.509766,2380.793701,2383.389160,2377.426270,2377.271484</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:53</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2501.056396,2498.822998,2497.289795,2494.726074,2493.151367,2492.752197</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2494.822510,2493.768555,2495.204346,2489.083252,2482.336182,2480.907227</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2476.604004,2471.914307,2460.843750,2455.443604,2450.027588,2443.186035</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2486.639648,2482.172119,2476.049805,2470.669434,2464.850342,2461.594727</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>2492.752197265625</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2452.669921875</v>
+      </c>
+      <c r="H48" t="n">
+        <v>40.082275390625</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.63423031501863</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.548017453935798</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:49</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2443.9794921875</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>2501.056396,2498.822998,2497.289795,2494.726074,2493.151367,2492.752197</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2522.979980,2452.080078,2456.479980,2456.070068,2452.840088,2452.669922</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>21.923584,46.742920,40.809815,38.656006,40.311279,40.082275</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.868956,1.906256,1.661313,1.573897,1.643453,1.634230</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.548017453935798</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>2494.822510,2493.768555,2495.204346,2489.083252,2482.336182,2480.907227</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>2486.639648,2482.172119,2476.049805,2470.669434,2464.850342,2461.594727</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:49</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2456.026855,2452.229004,2449.282227,2448.000977,2444.620605,2443.979492</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2452.782227,2452.140137,2445.414062,2442.397949,2438.900391,2433.183105</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2428.601074,2419.462891,2408.330566,2405.299805,2394.744141,2390.105957</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2439.784668,2431.388184,2424.460938,2420.705322,2412.717773,2412.040039</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>2443.9794921875</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2506.989990234375</v>
+      </c>
+      <c r="H49" t="n">
+        <v>63.010498046875</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.513392486301241</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.346870793029592</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:40</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2489.822998046875</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>2456.026855,2452.229004,2449.282227,2448.000977,2444.620605,2443.979492</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2453.699951,2460.409912,2477.679932,2482.830078,2509.659912,2506.989990</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2.326904,8.180908,28.397705,34.829101,65.039307,63.010498</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.094832,0.332502,1.146141,1.402798,2.591559,2.513392</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1.346870793029592</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>2452.782227,2452.140137,2445.414062,2442.397949,2438.900391,2433.183105</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>2439.784668,2431.388184,2424.460938,2420.705322,2412.717773,2412.040039</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:40</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2507.246338,2502.626465,2499.189697,2494.918701,2490.424805,2489.822998</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2503.616943,2497.568359,2493.955566,2487.679932,2481.269287,2477.850342</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2473.540527,2463.777588,2452.074463,2447.498779,2436.987793,2434.849854</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2486.602295,2477.679688,2470.699463,2464.865479,2456.177490,2455.842285</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>2489.822998046875</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2497.659912109375</v>
+      </c>
+      <c r="H50" t="n">
+        <v>7.8369140625</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.3137702624966827</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.4755755710782296</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:57</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2493.787353515625</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>2507.246338,2502.626465,2499.189697,2494.918701,2490.424805,2489.822998</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2502.239990,2479.850098,2490.500000,2514.860107,2497.399902,2497.659912</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5.006348,22.776367,8.689697,19.941406,6.975097,7.836914</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.200075,0.918457,0.348914,0.792943,0.279294,0.313770</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.4755755710782296</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>2503.616943,2497.568359,2493.955566,2487.679932,2481.269287,2477.850342</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>2486.602295,2477.679688,2470.699463,2464.865479,2456.177490,2455.842285</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:57</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2495.416748,2495.665771,2492.234619,2489.443115,2489.571533,2493.787354</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2490.179199,2493.411377,2491.181641,2485.299316,2488.232422,2480.386719</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2459.561035,2460.129639,2451.046631,2449.447998,2445.696533,2451.307129</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2472.267090,2471.185303,2466.168701,2462.682617,2460.499756,2464.705566</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>2493.787353515625</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2482.639892578125</v>
+      </c>
+      <c r="H51" t="n">
+        <v>11.1474609375</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.4490164268618029</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3441527007023585</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:44</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2480.197021484375</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>2495.416748,2495.665771,2492.234619,2489.443115,2489.571533,2493.787354</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2488.989990,2470.030029,2495.820068,2489.570068,2485.320068,2482.639893</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6.426758,25.635742,3.585449,0.126953,4.251465,11.147461</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.258207,1.037872,0.143658,0.005099,0.171063,0.449016</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3441527007023585</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>2490.179199,2493.411377,2491.181641,2485.299316,2488.232422,2480.386719</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>2472.267090,2471.185303,2466.168701,2462.682617,2460.499756,2464.705566</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:44</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2487.569824,2487.318359,2481.225586,2480.178223,2477.780029,2480.197021</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2483.804443,2489.240967,2480.601074,2478.711670,2476.201904,2465.649902</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2463.173828,2461.801025,2449.764648,2449.533691,2443.174561,2444.658691</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2471.972900,2470.296387,2462.133789,2460.752197,2456.327148,2457.937500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>2480.197021484375</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2497.669921875</v>
+      </c>
+      <c r="H52" t="n">
+        <v>17.472900390625</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.6995680348950232</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.3958429962270238</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2489.50927734375</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>2487.569824,2487.318359,2481.225586,2480.178223,2477.780029,2480.197021</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2473.729980,2498.399902,2482.229980,2484.959961,2488.719971,2497.669922</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>13.839844,11.081543,1.004394,4.781738,10.939942,17.472901</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.559473,0.443546,0.040463,0.192427,0.439581,0.699568</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.3958429962270238</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>2483.804443,2489.240967,2480.601074,2478.711670,2476.201904,2465.649902</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>2471.972900,2470.296387,2462.133789,2460.752197,2456.327148,2457.937500</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2495.502930,2493.598145,2489.403809,2487.906738,2488.444824,2489.509277</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2491.592773,2494.863770,2487.006348,2487.192871,2489.236816,2479.917480</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2472.332520,2469.994629,2460.224121,2460.064941,2457.803223,2457.217773</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2481.525879,2478.968262,2472.509766,2470.850586,2469.159668,2470.496582</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>2489.50927734375</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2476.830078125</v>
+      </c>
+      <c r="H53" t="n">
+        <v>12.67919921875</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5119123564725262</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5366499839231</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:10</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2470.073486328125</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>2495.502930,2493.598145,2489.403809,2487.906738,2488.444824,2489.509277</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2500.149902,2489.850098,2465.000000,2467.719971,2474.500000,2476.830078</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4.646972,3.748047,24.403809,20.186767,13.944824,12.679199</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.185868,0.150533,0.990013,0.818033,0.563541,0.511912</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5366499839231</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>2491.592773,2494.863770,2487.006348,2487.192871,2489.236816,2479.917480</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>2481.525879,2478.968262,2472.509766,2470.850586,2469.159668,2470.496582</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:10</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2470.019287,2470.926270,2468.303955,2467.902832,2470.038818,2470.073486</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2466.512207,2471.807617,2466.232666,2455.900635,2471.593750,2465.718506</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2451.748047,2450.161865,2439.771240,2436.526855,2432.589844,2427.708740</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2457.554932,2458.621582,2452.351318,2449.266113,2448.487305,2447.569824</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>2470.073486328125</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2450.27001953125</v>
+      </c>
+      <c r="H54" t="n">
+        <v>19.803466796875</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.8082156921082319</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.8170694366137379</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:55</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2451.933349609375</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>2470.019287,2470.926270,2468.303955,2467.902832,2470.038818,2470.073486</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2461.500000,2440.439941,2461.790039,2437.209961,2446.189941,2450.270020</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8.519287,30.486329,6.513916,30.692871,23.848877,19.803466</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.346101,1.249214,0.264601,1.259345,0.974940,0.808216</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.8170694366137379</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>2466.512207,2471.807617,2466.232666,2455.900635,2471.593750,2465.718506</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>2457.554932,2458.621582,2452.351318,2449.266113,2448.487305,2447.569824</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:55</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2446.536621,2447.500000,2446.577148,2447.587646,2450.345947,2451.933350</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2444.651367,2446.335449,2436.741455,2437.328369,2449.841553,2440.505127</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2424.563232,2422.270020,2415.808838,2414.656250,2411.445557,2409.312988</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2432.384277,2431.217285,2428.235840,2427.852783,2426.994385,2428.115479</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>2451.933349609375</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2511.8701171875</v>
+      </c>
+      <c r="H55" t="n">
+        <v>59.936767578125</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.386141192890786</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.676121335126215</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2495.97607421875</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>2446.536621,2447.500000,2446.577148,2447.587646,2450.345947,2451.933350</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2457.610107,2559.320068,2538.969971,2516.100098,2512.889893,2511.870117</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>11.073486,111.820068,92.392823,68.512452,62.543946,59.936767</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.450579,4.369132,3.638988,2.722962,2.488925,2.386141</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2.676121335126215</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>2444.651367,2446.335449,2436.741455,2437.328369,2449.841553,2440.505127</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>2432.384277,2431.217285,2428.235840,2427.852783,2426.994385,2428.115479</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2508.615723,2498.887207,2500.500488,2491.285400,2500.025146,2495.976074</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2497.724121,2494.609619,2486.855957,2484.924072,2498.440918,2479.211182</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2481.740967,2461.570068,2463.281982,2452.238037,2456.990479,2448.659180</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2488.045898,2474.351318,2479.416504,2468.171875,2478.136475,2467.635742</t>
         </is>
       </c>
     </row>
